--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -413,9 +413,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PR Number</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Create list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>PR Number</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,7 +429,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Author</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Files Changed</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Additions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Deletions</t>
         </is>
       </c>
     </row>
@@ -442,10 +462,20 @@
           <t>Create list_prs.yml</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Mounashree-2310</t>
         </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -462,7 +462,19 @@
           <t>Create list_prs.yml</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Developed a GitHub Pull Request Tool.
+Features:
+1. Extract PR Details
+2. Update PR Description
+3. List Last N PRs
+4. Generate JSON Report
+5. Generate Excel Report
+number_of_prs=25
+repo_url=https://github.com/Mounashree-2310/Python_tool</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Mounashree-2310</t>
@@ -472,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -415,6 +415,15 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="254" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -418,11 +418,11 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="254" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,12 +453,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Additions</t>
+          <t>Files Added</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Deletions</t>
+          <t>Files Deleted</t>
         </is>
       </c>
     </row>
@@ -473,15 +473,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Developed a GitHub Pull Request Tool.
-Features:
-1. Extract PR Details
-2. Update PR Description
-3. List Last N PRs
-4. Generate JSON Report
-5. Generate Excel Report
-number_of_prs=25
-repo_url=https://github.com/Mounashree-2310/Python_tool</t>
+          <t>Pull Request Automation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -413,22 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>PR Number</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -438,57 +434,158 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>Author</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Files Changed</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Files Added</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Files Deleted</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Update README.md</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Create list_prs.yml</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pull Request Automation</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F2" t="n">
-        <v>180</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/pr_report.xlsx
+++ b/pr_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -573,21 +573,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Create list_prs.yml</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mounashree-2310</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
